--- a/data/trans_dic/IP44C$ninguna_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que no han tenido retrasos en pagos</t>
+          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,81; 81,27</t>
+          <t>54,68; 83,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,07; 79,29</t>
+          <t>59,35; 80,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,77; 77,91</t>
+          <t>59,95; 78,12</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>59,64; 84,85</t>
+          <t>65,53; 84,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,46; 86,67</t>
+          <t>80,33; 86,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,33; 84,46</t>
+          <t>72,9; 84,46</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,71; 96,68</t>
+          <t>89,86; 96,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>92,22; 97,36</t>
+          <t>91,95; 97,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,22; 96,48</t>
+          <t>91,96; 96,33</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>69,67; 85,76</t>
+          <t>69,35; 85,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,95; 87,47</t>
+          <t>82,9; 87,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,11; 85,81</t>
+          <t>77,02; 85,75</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>36153</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42287</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>78441</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>28542; 43441</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>35663; 48302</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>67320; 87722</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1056</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>354929</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>421207</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>776136</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>295362; 382672</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>404585; 435291</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>695777; 806083</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>139991</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>171669</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>311661</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>134042; 144164</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165769; 175328</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>302960; 317364</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1591</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>531074</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>635163</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1166237</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>452247; 560631</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>616796; 652291</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1075361; 1197165</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$ninguna_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,68; 83,22</t>
+          <t>51,81; 82,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,35; 80,38</t>
+          <t>59,0; 79,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,95; 78,12</t>
+          <t>60,75; 77,98</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>65,53; 84,89</t>
+          <t>61,87; 84,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,33; 86,42</t>
+          <t>80,44; 86,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,9; 84,46</t>
+          <t>72,66; 84,43</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,86; 96,65</t>
+          <t>89,23; 96,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,95; 97,25</t>
+          <t>91,6; 97,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91,96; 96,33</t>
+          <t>92,32; 96,44</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>69,35; 85,97</t>
+          <t>65,74; 85,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,9; 87,67</t>
+          <t>82,89; 87,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,02; 85,75</t>
+          <t>77,74; 85,92</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28542; 43441</t>
+          <t>27047; 42839</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35663; 48302</t>
+          <t>35454; 47839</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67320; 87722</t>
+          <t>68217; 87572</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>295362; 382672</t>
+          <t>278871; 382289</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>404585; 435291</t>
+          <t>405135; 436666</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>695777; 806083</t>
+          <t>693516; 805851</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>134042; 144164</t>
+          <t>133099; 144038</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>165769; 175328</t>
+          <t>165135; 175464</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>302960; 317364</t>
+          <t>304129; 317733</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>452247; 560631</t>
+          <t>428690; 559367</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>616796; 652291</t>
+          <t>616709; 652008</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1075361; 1197165</t>
+          <t>1085398; 1199550</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$ninguna_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,81; 82,07</t>
+          <t>57,64; 77,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,0; 79,61</t>
+          <t>56,23; 79,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,75; 77,98</t>
+          <t>60,28; 76,38</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>61,87; 84,81</t>
+          <t>80,18; 86,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80,44; 86,7</t>
+          <t>79,08; 85,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,66; 84,43</t>
+          <t>80,72; 85,25</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>89,23; 96,57</t>
+          <t>91,57; 97,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,6; 97,33</t>
+          <t>89,37; 96,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,32; 96,44</t>
+          <t>91,73; 96,29</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>65,74; 85,78</t>
+          <t>82,46; 87,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,89; 87,63</t>
+          <t>81,19; 86,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,74; 85,92</t>
+          <t>82,7; 86,26</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36153</t>
+          <t>37450</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42287</t>
+          <t>30708</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78441</t>
+          <t>68157</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27047; 42839</t>
+          <t>31603; 42600</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35454; 47839</t>
+          <t>24980; 35323</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68217; 87572</t>
+          <t>59821; 75799</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>531</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>525</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>531</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>354929</t>
+          <t>385654</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421207</t>
+          <t>350260</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>776136</t>
+          <t>735914</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>278871; 382289</t>
+          <t>371084; 400036</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>405135; 436666</t>
+          <t>334404; 362794</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>693516; 805851</t>
+          <t>714953; 755072</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>215</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>139991</t>
+          <t>156746</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>171669</t>
+          <t>140138</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311661</t>
+          <t>296884</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>133099; 144038</t>
+          <t>151494; 160705</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>165135; 175464</t>
+          <t>133729; 144572</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>304129; 317733</t>
+          <t>289001; 303381</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>807</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>784</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>807</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>531074</t>
+          <t>579849</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>635163</t>
+          <t>521106</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1166237</t>
+          <t>1100955</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>428690; 559367</t>
+          <t>563302; 595555</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>616709; 652008</t>
+          <t>500868; 534917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1085398; 1199550</t>
+          <t>1075138; 1121333</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$ninguna_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$ninguna_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>68,31%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>69,13%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>68,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>57,64; 77,7</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>56,23; 79,52</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>60,28; 76,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>83,33%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>82,83%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>83,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>80,18; 86,43</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>79,08; 85,8</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>80,72; 85,25</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>94,75%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>94,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>91,57; 97,14</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>89,37; 96,62</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>91,73; 96,29</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>84,89%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>84,47%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>84,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>82,46; 87,19</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>81,19; 86,71</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>82,7; 86,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6830642836092704</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.6912905628405789</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.6867461960057057</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>37450</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>30708</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>68157</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.5764293227048786</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.562337751152116</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.6027570454359114</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>31603; 42600</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>24980; 35323</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>59821; 75799</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7770043767997009</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7951953879760481</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7637526790547686</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1056</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.833257007700857</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.8283352786011672</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.8309072258912277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>385654</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>350260</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>735914</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.801777304096814</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.7908379027518839</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8072413108200253</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>371084; 400036</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>334404; 362794</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>714953; 755072</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.8643319099488318</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.8579776378584</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.8525387628954972</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9474864069169774</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9365264418889536</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9422811849825856</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>156746</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>140138</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>296884</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.9157421360055327</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.8936967397741463</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.9172621104083052</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>151494; 160705</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>133729; 144572</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>289001; 303381</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9714181945911411</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9661597741418564</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9629045445019334</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>807</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1591</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8488669378034289</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8447100853252083</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8468943225906154</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>579849</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>521106</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1100955</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8246427522928514</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.8119040574921438</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8270347586994315</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>563302; 595555</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>500868; 534917</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1075138; 1121333</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.8718596627219037</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.8670979684719515</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.8625700402158752</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que no han tenido retrasos en pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>37450</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>30708</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>68157</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>31603</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>24980</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>59821</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>42600</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>35323</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>75799</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>531</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>525</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>385654</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>350260</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>735914</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>371084</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>334404</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>714953</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>400036</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>362794</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>755072</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>222</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>156746</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>140138</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>296884</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>151494</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>133729</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>289001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>160705</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>144572</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>303381</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>807</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>784</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>579849</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>521106</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1100955</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>563302</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>500868</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1075138</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>595555</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>534917</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1121333</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>